--- a/Base-Dados-Desafio-D&A-01.xlsx
+++ b/Base-Dados-Desafio-D&A-01.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agenteinvest-my.sharepoint.com/personal/silvio_000295_agenteinvest_com_br/Documents/TI/Equipe/Desafio Analista de Dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anaju\OneDrive\Área de Trabalho\Ana Julia\ana\DesafioManchester\desafio-data-analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="8_{82B762CB-491B-4169-9A41-6B17E63B7CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC273609-AEAA-4EF4-A796-96CE042C128A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2340" windowWidth="29040" windowHeight="15840" xr2:uid="{A58A9A92-5A66-4265-A839-C8670248DF81}"/>
+    <workbookView xWindow="-28920" yWindow="-2340" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="VENDAS" sheetId="1" r:id="rId1"/>
@@ -114,7 +113,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -460,18 +459,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE054DA-47BA-4D13-8F91-7CDEF0586101}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="1" max="2" width="9.109375" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -491,7 +490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -511,7 +510,7 @@
         <v>44201</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -532,7 +531,7 @@
         <v>44211</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -553,7 +552,7 @@
         <v>44221</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -574,7 +573,7 @@
         <v>44231</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -595,7 +594,7 @@
         <v>44241</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -616,7 +615,7 @@
         <v>44251</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -637,7 +636,7 @@
         <v>44261</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -658,7 +657,7 @@
         <v>44271</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -678,7 +677,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -699,7 +698,7 @@
         <v>44311</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>3</v>
       </c>
@@ -720,7 +719,7 @@
         <v>44321</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>3</v>
       </c>
@@ -741,7 +740,7 @@
         <v>44331</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>3</v>
       </c>
@@ -762,7 +761,7 @@
         <v>44341</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>3</v>
       </c>
@@ -782,7 +781,7 @@
         <v>44361</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
@@ -803,7 +802,7 @@
         <v>44371</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
@@ -824,7 +823,7 @@
         <v>44381</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>4</v>
       </c>
@@ -844,7 +843,7 @@
         <v>44411</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>4</v>
       </c>
@@ -865,7 +864,7 @@
         <v>44421</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>4</v>
       </c>
@@ -886,7 +885,7 @@
         <v>44431</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>5</v>
       </c>
@@ -907,7 +906,7 @@
         <v>44441</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>5</v>
       </c>
@@ -928,7 +927,7 @@
         <v>44451</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>5</v>
       </c>
@@ -948,7 +947,7 @@
         <v>44261</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>5</v>
       </c>
@@ -969,7 +968,7 @@
         <v>44271</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>5</v>
       </c>
@@ -990,7 +989,7 @@
         <v>44281</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
@@ -1010,7 +1009,7 @@
         <v>44431</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>6</v>
       </c>
@@ -1030,7 +1029,7 @@
         <v>44431</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>6</v>
       </c>
@@ -1050,7 +1049,7 @@
         <v>44331</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>6</v>
       </c>
@@ -1070,7 +1069,7 @@
         <v>44431</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>7</v>
       </c>
@@ -1090,7 +1089,7 @@
         <v>44201</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>7</v>
       </c>
@@ -1110,7 +1109,7 @@
         <v>44211</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>7</v>
       </c>
@@ -1130,7 +1129,7 @@
         <v>44221</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>7</v>
       </c>
@@ -1150,7 +1149,7 @@
         <v>44231</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>8</v>
       </c>
@@ -1170,7 +1169,7 @@
         <v>44271</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>8</v>
       </c>
@@ -1190,7 +1189,7 @@
         <v>44301</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>8</v>
       </c>
@@ -1210,7 +1209,7 @@
         <v>44311</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>8</v>
       </c>
@@ -1237,15 +1236,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4294DF6B-30AB-4FFA-81E2-8D657246E5C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -1253,7 +1252,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1261,7 +1260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1269,7 +1268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1277,7 +1276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1285,7 +1284,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
